--- a/data/trans_orig/P17A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P17A-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consultado con algún médico (público o privado) por agún problema, molestia o enfermedad suya en las últimas dos semanas en 2007</t>
+          <t>Población que ha tenido una consulta médica (pública o privada) por algún problema, molestia o enfermedad suya en las últimas 2 semanas en 2007 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43815</t>
+          <t>42643</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71309</t>
+          <t>71175</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>69831</t>
+          <t>70947</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>101731</t>
+          <t>102802</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>121112</t>
+          <t>120971</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>163681</t>
+          <t>164383</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,11%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>421905</t>
+          <t>422039</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>449399</t>
+          <t>450571</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>365758</t>
+          <t>364687</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>397658</t>
+          <t>396542</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>797022</t>
+          <t>796320</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>839591</t>
+          <t>839732</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,41%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56715</t>
+          <t>56760</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>91176</t>
+          <t>91692</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>128000</t>
+          <t>130329</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>172035</t>
+          <t>174434</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>195629</t>
+          <t>195406</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>250303</t>
+          <t>251860</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,52%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>643428</t>
+          <t>642912</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>677889</t>
+          <t>677844</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>453459</t>
+          <t>451060</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>497494</t>
+          <t>495165</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1109795</t>
+          <t>1108238</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1164469</t>
+          <t>1164692</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,63%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>77750</t>
+          <t>77125</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>113638</t>
+          <t>113741</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>162642</t>
+          <t>162877</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>210137</t>
+          <t>209321</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>250309</t>
+          <t>252212</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>310191</t>
+          <t>310101</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,38%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>525030</t>
+          <t>524927</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>560918</t>
+          <t>561543</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>477595</t>
+          <t>478411</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>525090</t>
+          <t>524855</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1016208</t>
+          <t>1016298</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1076090</t>
+          <t>1074187</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>80,99%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64533</t>
+          <t>66771</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>97819</t>
+          <t>100222</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>127998</t>
+          <t>129049</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>169484</t>
+          <t>167248</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>204500</t>
+          <t>204064</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>255304</t>
+          <t>255746</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,71%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>421328</t>
+          <t>418925</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>454614</t>
+          <t>452376</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>346158</t>
+          <t>348394</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>387644</t>
+          <t>386593</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>779485</t>
+          <t>779043</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>830289</t>
+          <t>830725</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>80,28%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>107940</t>
+          <t>108669</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>144527</t>
+          <t>143427</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>129220</t>
+          <t>131086</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>170175</t>
+          <t>170596</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>251761</t>
+          <t>251686</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>303980</t>
+          <t>302648</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,28%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>242183</t>
+          <t>243283</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>278770</t>
+          <t>278041</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>233811</t>
+          <t>233390</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>274766</t>
+          <t>272900</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>486716</t>
+          <t>488048</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>538935</t>
+          <t>539010</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>68,17%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>116027</t>
+          <t>118325</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>150417</t>
+          <t>151259</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>143573</t>
+          <t>145081</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>178690</t>
+          <t>180077</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>271837</t>
+          <t>272713</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>322684</t>
+          <t>320265</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>50,47%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>141232</t>
+          <t>140390</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>175622</t>
+          <t>173324</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>164244</t>
+          <t>162857</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>199361</t>
+          <t>197853</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>311899</t>
+          <t>314318</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>362746</t>
+          <t>361870</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>57,02%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>79748</t>
+          <t>78308</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>106701</t>
+          <t>107413</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>149140</t>
+          <t>146584</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>187764</t>
+          <t>187024</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>43,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>238029</t>
+          <t>236748</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>285152</t>
+          <t>282985</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>52,04%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>103182</t>
+          <t>102470</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>130135</t>
+          <t>131575</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>146144</t>
+          <t>146884</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>184768</t>
+          <t>187324</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>258639</t>
+          <t>260806</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>305762</t>
+          <t>307043</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>56,46%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>617762</t>
+          <t>610391</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>705959</t>
+          <t>701611</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>997604</t>
+          <t>989297</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1105986</t>
+          <t>1095103</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1636471</t>
+          <t>1642244</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1788573</t>
+          <t>1780854</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,78%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2567915</t>
+          <t>2572263</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2656112</t>
+          <t>2663483</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2271199</t>
+          <t>2282082</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2379581</t>
+          <t>2387888</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4862486</t>
+          <t>4870205</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5014588</t>
+          <t>5008815</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,31%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consultado con algún médico (público o privado) por agún problema, molestia o enfermedad suya en las últimas dos semanas en 2012</t>
+          <t>Población que ha tenido una consulta médica (pública o privada) por algún problema, molestia o enfermedad suya en las últimas 2 semanas en 2012 (tasa de respuesta: 99,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>45203</t>
+          <t>45329</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>74942</t>
+          <t>75054</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>81968</t>
+          <t>81477</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>117177</t>
+          <t>115941</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>135073</t>
+          <t>133375</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>181241</t>
+          <t>180358</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,52%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>378220</t>
+          <t>378108</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>407959</t>
+          <t>407833</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>308805</t>
+          <t>310041</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>344014</t>
+          <t>344505</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>697903</t>
+          <t>698786</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>744071</t>
+          <t>745769</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,83%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>81597</t>
+          <t>83223</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>118120</t>
+          <t>120341</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>143006</t>
+          <t>141665</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>186997</t>
+          <t>186436</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>235725</t>
+          <t>233980</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>295955</t>
+          <t>295882</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>565123</t>
+          <t>562902</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>601646</t>
+          <t>600020</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>421404</t>
+          <t>421965</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>465395</t>
+          <t>466736</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>995688</t>
+          <t>995761</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1055918</t>
+          <t>1057663</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>81,89%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>110006</t>
+          <t>107573</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>152576</t>
+          <t>150032</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>169127</t>
+          <t>169914</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>220614</t>
+          <t>218947</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>291432</t>
+          <t>290772</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>354701</t>
+          <t>354241</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,54%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>525403</t>
+          <t>527947</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>567973</t>
+          <t>570406</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>488363</t>
+          <t>490030</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>539850</t>
+          <t>539063</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1032255</t>
+          <t>1032715</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1095524</t>
+          <t>1096184</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>79,04%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>94116</t>
+          <t>94231</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>136910</t>
+          <t>135609</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>172229</t>
+          <t>169161</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>220954</t>
+          <t>218128</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>273090</t>
+          <t>276238</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>343105</t>
+          <t>342699</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,87%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>477707</t>
+          <t>479008</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>520501</t>
+          <t>520386</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>394163</t>
+          <t>396989</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>442888</t>
+          <t>445956</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>72,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>886629</t>
+          <t>887035</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>956644</t>
+          <t>953496</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,54%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>110305</t>
+          <t>111502</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>149669</t>
+          <t>151174</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>141279</t>
+          <t>139433</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>184901</t>
+          <t>181435</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>261227</t>
+          <t>264106</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>319197</t>
+          <t>319357</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,53%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>276721</t>
+          <t>275216</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>316085</t>
+          <t>314888</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>262899</t>
+          <t>266365</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>306521</t>
+          <t>308367</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>554993</t>
+          <t>554833</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>612963</t>
+          <t>610084</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>69,79%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>115667</t>
+          <t>118700</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>155354</t>
+          <t>154517</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>135367</t>
+          <t>134970</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>172909</t>
+          <t>172763</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>261116</t>
+          <t>265168</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>313927</t>
+          <t>316714</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>47,86%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>153422</t>
+          <t>154259</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>193109</t>
+          <t>190076</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>180078</t>
+          <t>180224</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>217620</t>
+          <t>218017</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>347836</t>
+          <t>345049</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>400647</t>
+          <t>396595</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>52,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>59,93%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>97052</t>
+          <t>97894</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>129570</t>
+          <t>130610</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>170487</t>
+          <t>168079</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>211521</t>
+          <t>209505</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>281594</t>
+          <t>281518</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>333270</t>
+          <t>332859</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>52,28%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>119126</t>
+          <t>118086</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>151644</t>
+          <t>150802</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>176453</t>
+          <t>178469</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>217487</t>
+          <t>219895</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>303401</t>
+          <t>303812</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>355077</t>
+          <t>355153</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>55,78%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>727602</t>
+          <t>730173</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>831428</t>
+          <t>831885</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1099220</t>
+          <t>1101719</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1215417</t>
+          <t>1213743</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1852918</t>
+          <t>1869143</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2008479</t>
+          <t>2015001</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,95%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2581435</t>
+          <t>2580978</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2685261</t>
+          <t>2682690</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2331821</t>
+          <t>2333495</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2448018</t>
+          <t>2445519</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4951622</t>
+          <t>4945100</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5107183</t>
+          <t>5090958</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>73,14%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consultado con algún médico (público o privado) por agún problema, molestia o enfermedad suya en las últimas dos semanas en 2016</t>
+          <t>Población que ha tenido una consulta médica (pública o privada) por algún problema, molestia o enfermedad suya en las últimas 2 semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>55191</t>
+          <t>55047</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>83276</t>
+          <t>82749</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>78906</t>
+          <t>76264</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>110429</t>
+          <t>110327</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>140042</t>
+          <t>139654</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>184558</t>
+          <t>184044</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,58%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>336187</t>
+          <t>336714</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>364272</t>
+          <t>364416</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>285326</t>
+          <t>285428</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>316849</t>
+          <t>319491</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>630660</t>
+          <t>631174</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>675176</t>
+          <t>675564</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>82,87%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>74934</t>
+          <t>73768</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>109694</t>
+          <t>110017</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>137004</t>
+          <t>137794</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>177613</t>
+          <t>179825</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>223404</t>
+          <t>222443</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>276874</t>
+          <t>279353</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,21%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>480802</t>
+          <t>480479</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>515562</t>
+          <t>516728</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>385931</t>
+          <t>383719</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>426540</t>
+          <t>425750</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>877166</t>
+          <t>874687</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>930636</t>
+          <t>931597</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,72%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>126192</t>
+          <t>126468</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>168857</t>
+          <t>168759</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>151232</t>
+          <t>152403</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>197185</t>
+          <t>197375</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>290659</t>
+          <t>289625</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>356014</t>
+          <t>355699</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,73%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>500240</t>
+          <t>500338</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>542905</t>
+          <t>542629</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>464201</t>
+          <t>464011</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>510154</t>
+          <t>508983</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>974469</t>
+          <t>974784</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1039824</t>
+          <t>1040858</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>78,23%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>142057</t>
+          <t>144412</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>188949</t>
+          <t>189582</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>158627</t>
+          <t>159465</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>205668</t>
+          <t>204570</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>316474</t>
+          <t>315835</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>381784</t>
+          <t>381129</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,43%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>457099</t>
+          <t>456466</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>503991</t>
+          <t>501636</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>443409</t>
+          <t>444507</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>490450</t>
+          <t>489612</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>913341</t>
+          <t>913996</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>978651</t>
+          <t>979290</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,61%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>124828</t>
+          <t>125450</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>165498</t>
+          <t>166033</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>174218</t>
+          <t>172640</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>219612</t>
+          <t>218148</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>310840</t>
+          <t>308239</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>368942</t>
+          <t>374244</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>38,39%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>312420</t>
+          <t>311885</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>353090</t>
+          <t>352468</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>277237</t>
+          <t>278701</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>322631</t>
+          <t>324209</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>56,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>605825</t>
+          <t>600523</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>663927</t>
+          <t>666528</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>68,38%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>113351</t>
+          <t>114836</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>149337</t>
+          <t>147797</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>165886</t>
+          <t>165386</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>203038</t>
+          <t>206634</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>293468</t>
+          <t>290656</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>345184</t>
+          <t>345240</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>48,48%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>184993</t>
+          <t>186533</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>220979</t>
+          <t>219494</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>174724</t>
+          <t>171128</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>211876</t>
+          <t>212376</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>56,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>366908</t>
+          <t>366852</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>418624</t>
+          <t>421436</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>59,18%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>94073</t>
+          <t>94870</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>122046</t>
+          <t>122601</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>155318</t>
+          <t>153628</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>198853</t>
+          <t>199227</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>257558</t>
+          <t>256378</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>310731</t>
+          <t>311948</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>47,47%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>134952</t>
+          <t>134397</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>162925</t>
+          <t>162128</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>52,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>201316</t>
+          <t>200942</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>244851</t>
+          <t>246541</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>346436</t>
+          <t>345219</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>399609</t>
+          <t>400789</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>52,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>60,99%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>798675</t>
+          <t>799914</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>905200</t>
+          <t>906779</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1104722</t>
+          <t>1110662</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1218369</t>
+          <t>1227594</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1942331</t>
+          <t>1941723</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2101129</t>
+          <t>2090482</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,13%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2489150</t>
+          <t>2487571</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2595675</t>
+          <t>2594436</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2326173</t>
+          <t>2316948</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2439820</t>
+          <t>2433880</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>65,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4837763</t>
+          <t>4848410</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4996561</t>
+          <t>4997169</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>72,02%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consultado con algún médico (público o privado) por agún problema, molestia o enfermedad suya en las últimas dos semanas en 2023</t>
+          <t>Población que ha tenido una consulta médica (pública o privada) por algún problema, molestia o enfermedad suya en las últimas 2 semanas en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17147</t>
+          <t>15629</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>57801</t>
+          <t>58490</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38128</t>
+          <t>38519</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>73461</t>
+          <t>76571</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>62561</t>
+          <t>62951</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>119341</t>
+          <t>117097</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>342186</t>
+          <t>341497</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>382840</t>
+          <t>384358</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>239739</t>
+          <t>236629</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>275072</t>
+          <t>274681</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>593846</t>
+          <t>596090</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>650626</t>
+          <t>650236</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,17%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59573</t>
+          <t>59413</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>98411</t>
+          <t>102201</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>106422</t>
+          <t>106692</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>306082</t>
+          <t>303343</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>179624</t>
+          <t>180437</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>417348</t>
+          <t>418175</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>44,78%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>325136</t>
+          <t>321346</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>363974</t>
+          <t>364134</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>204139</t>
+          <t>206878</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>403799</t>
+          <t>403529</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>516420</t>
+          <t>515593</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>754144</t>
+          <t>753331</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>55,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,68%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>63948</t>
+          <t>64430</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>98650</t>
+          <t>98447</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>102651</t>
+          <t>103545</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>135622</t>
+          <t>134135</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>177369</t>
+          <t>176488</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>223120</t>
+          <t>223961</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,76%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>437688</t>
+          <t>437891</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>472390</t>
+          <t>471908</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>406846</t>
+          <t>408333</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>439817</t>
+          <t>438923</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>855686</t>
+          <t>854845</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>901437</t>
+          <t>902318</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,64%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53539</t>
+          <t>57687</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>186430</t>
+          <t>184240</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>142280</t>
+          <t>142879</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>189301</t>
+          <t>190172</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>176176</t>
+          <t>178891</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>357660</t>
+          <t>363089</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,69%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>701356</t>
+          <t>703546</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>834247</t>
+          <t>830099</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>523168</t>
+          <t>522297</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>570189</t>
+          <t>569590</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1242595</t>
+          <t>1237166</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1424079</t>
+          <t>1421364</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>88,82%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>119145</t>
+          <t>121486</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>157705</t>
+          <t>158114</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>124159</t>
+          <t>125720</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>154904</t>
+          <t>155008</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>255322</t>
+          <t>252790</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>301551</t>
+          <t>302719</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,3%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>403529</t>
+          <t>403120</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>442089</t>
+          <t>439748</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>78,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>392560</t>
+          <t>392456</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>423305</t>
+          <t>421744</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>807147</t>
+          <t>805979</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>853376</t>
+          <t>855908</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>77,2%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>91020</t>
+          <t>91320</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>119064</t>
+          <t>118373</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>49134</t>
+          <t>47256</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>189463</t>
+          <t>192846</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>113351</t>
+          <t>110506</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>295964</t>
+          <t>293100</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,06%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>248480</t>
+          <t>249171</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>276524</t>
+          <t>276224</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>417916</t>
+          <t>414533</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>558245</t>
+          <t>560123</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>678960</t>
+          <t>681824</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>861573</t>
+          <t>864418</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,67%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>69042</t>
+          <t>68503</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>93485</t>
+          <t>92305</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>115588</t>
+          <t>115124</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>141564</t>
+          <t>142108</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>191727</t>
+          <t>189624</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>227012</t>
+          <t>225910</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>31,94%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>188457</t>
+          <t>189637</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>212900</t>
+          <t>213439</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>283868</t>
+          <t>283324</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>309844</t>
+          <t>310308</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>480362</t>
+          <t>481464</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>515647</t>
+          <t>517750</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>73,19%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>487465</t>
+          <t>483831</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>704610</t>
+          <t>712631</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>765541</t>
+          <t>758693</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1041671</t>
+          <t>1050300</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1356635</t>
+          <t>1355095</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1718072</t>
+          <t>1718603</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,15%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2753769</t>
+          <t>2745748</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2970914</t>
+          <t>2974548</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2616962</t>
+          <t>2608333</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2893092</t>
+          <t>2899940</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5398940</t>
+          <t>5398409</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5760377</t>
+          <t>5761917</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>80,96%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P17A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P17A-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42643</t>
+          <t>42755</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71175</t>
+          <t>71776</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>70947</t>
+          <t>69220</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>102802</t>
+          <t>103268</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>120971</t>
+          <t>119016</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>164383</t>
+          <t>163896</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>422039</t>
+          <t>421438</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>450571</t>
+          <t>450459</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>364687</t>
+          <t>364221</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>396542</t>
+          <t>398269</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>796320</t>
+          <t>796807</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>839732</t>
+          <t>841687</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,61%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56760</t>
+          <t>57951</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>91692</t>
+          <t>90123</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>130329</t>
+          <t>128375</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>174434</t>
+          <t>174991</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>195406</t>
+          <t>197142</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>251860</t>
+          <t>251358</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,48%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>642912</t>
+          <t>644481</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>677844</t>
+          <t>676653</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>451060</t>
+          <t>450503</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>495165</t>
+          <t>497119</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1108238</t>
+          <t>1108740</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1164692</t>
+          <t>1162956</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,51%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>77125</t>
+          <t>75554</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>113741</t>
+          <t>112891</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>162877</t>
+          <t>163918</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>209321</t>
+          <t>210722</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>252212</t>
+          <t>249281</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>310101</t>
+          <t>311258</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,47%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>524927</t>
+          <t>525777</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>561543</t>
+          <t>563114</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>478411</t>
+          <t>477010</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>524855</t>
+          <t>523814</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1016298</t>
+          <t>1015141</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1074187</t>
+          <t>1077118</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>81,21%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66771</t>
+          <t>65474</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>100222</t>
+          <t>99447</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>129049</t>
+          <t>127014</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>167248</t>
+          <t>169313</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>204064</t>
+          <t>200541</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>255746</t>
+          <t>256647</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,8%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>418925</t>
+          <t>419700</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>452376</t>
+          <t>453673</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>348394</t>
+          <t>346329</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>386593</t>
+          <t>388628</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>75,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>779043</t>
+          <t>778142</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>830725</t>
+          <t>834248</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>80,62%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>108669</t>
+          <t>110172</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>143427</t>
+          <t>144834</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>131086</t>
+          <t>131183</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>170596</t>
+          <t>169427</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>251686</t>
+          <t>250991</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>302648</t>
+          <t>302822</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,3%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>243283</t>
+          <t>241876</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>278041</t>
+          <t>276538</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>233390</t>
+          <t>234559</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>272900</t>
+          <t>272803</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>488048</t>
+          <t>487874</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>539010</t>
+          <t>539705</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>68,26%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>118325</t>
+          <t>118591</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>151259</t>
+          <t>152673</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>145081</t>
+          <t>144934</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>180077</t>
+          <t>179778</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>272713</t>
+          <t>272160</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>320265</t>
+          <t>321999</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>50,74%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>140390</t>
+          <t>138976</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>173324</t>
+          <t>173058</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>59,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>162857</t>
+          <t>163156</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>197853</t>
+          <t>198000</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>314318</t>
+          <t>312584</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>361870</t>
+          <t>362423</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>57,11%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>78308</t>
+          <t>79733</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>107413</t>
+          <t>107498</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>146584</t>
+          <t>148255</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>187024</t>
+          <t>187116</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>236748</t>
+          <t>234656</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>282985</t>
+          <t>283341</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>52,1%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>102470</t>
+          <t>102385</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>131575</t>
+          <t>130150</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>48,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>146884</t>
+          <t>146792</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>187324</t>
+          <t>185653</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>260806</t>
+          <t>260450</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>307043</t>
+          <t>309135</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>56,85%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>610391</t>
+          <t>615137</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>701611</t>
+          <t>706471</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>989297</t>
+          <t>994968</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1095103</t>
+          <t>1102982</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1642244</t>
+          <t>1635480</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1780854</t>
+          <t>1776710</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,71%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2572263</t>
+          <t>2567403</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2663483</t>
+          <t>2658737</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2282082</t>
+          <t>2274203</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2387888</t>
+          <t>2382217</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4870205</t>
+          <t>4874349</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5008815</t>
+          <t>5015579</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,41%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>45329</t>
+          <t>45408</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>75054</t>
+          <t>74304</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>81477</t>
+          <t>79293</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>115941</t>
+          <t>115596</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>133375</t>
+          <t>134805</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>180358</t>
+          <t>179424</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,41%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>378108</t>
+          <t>378858</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>407833</t>
+          <t>407754</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>310041</t>
+          <t>310386</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>344505</t>
+          <t>346689</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>698786</t>
+          <t>699720</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>745769</t>
+          <t>744339</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,67%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>83223</t>
+          <t>83347</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>120341</t>
+          <t>120186</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>141665</t>
+          <t>143020</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>186436</t>
+          <t>187167</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>233980</t>
+          <t>233662</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>295882</t>
+          <t>293406</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,72%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>562902</t>
+          <t>563057</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>600020</t>
+          <t>599896</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>421965</t>
+          <t>421234</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>466736</t>
+          <t>465381</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>995761</t>
+          <t>998237</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1057663</t>
+          <t>1057981</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>81,91%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>107573</t>
+          <t>108811</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>150032</t>
+          <t>152132</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>169914</t>
+          <t>169770</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>218947</t>
+          <t>217213</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>290772</t>
+          <t>292256</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>354241</t>
+          <t>354964</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,59%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>527947</t>
+          <t>525847</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>570406</t>
+          <t>569168</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>490030</t>
+          <t>491764</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>539063</t>
+          <t>539207</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1032715</t>
+          <t>1031992</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1096184</t>
+          <t>1094700</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>74,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>78,93%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>94231</t>
+          <t>95193</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>135609</t>
+          <t>135119</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>169161</t>
+          <t>170546</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>218128</t>
+          <t>218134</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>276238</t>
+          <t>275469</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>342699</t>
+          <t>338363</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,52%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>479008</t>
+          <t>479498</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>520386</t>
+          <t>519424</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>396989</t>
+          <t>396983</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>445956</t>
+          <t>444571</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>887035</t>
+          <t>891371</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>953496</t>
+          <t>954265</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,6%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>111502</t>
+          <t>110004</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>151174</t>
+          <t>151074</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>139433</t>
+          <t>141622</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>181435</t>
+          <t>182557</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>264106</t>
+          <t>263571</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>319357</t>
+          <t>322059</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,84%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>275216</t>
+          <t>275316</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>314888</t>
+          <t>316386</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>266365</t>
+          <t>265243</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>308367</t>
+          <t>306178</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>554833</t>
+          <t>552131</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>610084</t>
+          <t>610619</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,85%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>118700</t>
+          <t>116565</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>154517</t>
+          <t>154238</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>134970</t>
+          <t>135154</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>172763</t>
+          <t>172135</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>265168</t>
+          <t>263038</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>316714</t>
+          <t>313998</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>47,45%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>154259</t>
+          <t>154538</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>190076</t>
+          <t>192211</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>180224</t>
+          <t>180852</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>218017</t>
+          <t>217833</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>345049</t>
+          <t>347765</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>396595</t>
+          <t>398725</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>60,25%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>97894</t>
+          <t>96370</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>130610</t>
+          <t>130908</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>168079</t>
+          <t>171208</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>209505</t>
+          <t>210521</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>281518</t>
+          <t>280633</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>332859</t>
+          <t>334093</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,48%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>118086</t>
+          <t>117788</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>150802</t>
+          <t>152326</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>178469</t>
+          <t>177453</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>219895</t>
+          <t>216766</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>303812</t>
+          <t>302578</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>355153</t>
+          <t>356038</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>55,92%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>730173</t>
+          <t>728996</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>831885</t>
+          <t>833045</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1101719</t>
+          <t>1099160</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1213743</t>
+          <t>1211669</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1869143</t>
+          <t>1859772</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2015001</t>
+          <t>2011120</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,89%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2580978</t>
+          <t>2579818</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2682690</t>
+          <t>2683867</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2333495</t>
+          <t>2335569</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2445519</t>
+          <t>2448078</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4945100</t>
+          <t>4948981</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5090958</t>
+          <t>5100329</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>73,28%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>55047</t>
+          <t>53479</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>82749</t>
+          <t>84297</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>76264</t>
+          <t>77611</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>110327</t>
+          <t>110138</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>139654</t>
+          <t>139150</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>184044</t>
+          <t>184870</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,68%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>336714</t>
+          <t>335166</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>364416</t>
+          <t>365984</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>285428</t>
+          <t>285617</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>319491</t>
+          <t>318144</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>631174</t>
+          <t>630348</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>675564</t>
+          <t>676068</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,93%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>73768</t>
+          <t>71649</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>110017</t>
+          <t>109451</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>137794</t>
+          <t>136975</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>179825</t>
+          <t>180096</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>222443</t>
+          <t>220237</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>279353</t>
+          <t>276171</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>23,93%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>480479</t>
+          <t>481045</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>516728</t>
+          <t>518847</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>383719</t>
+          <t>383448</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>425750</t>
+          <t>426569</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>68,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>874687</t>
+          <t>877869</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>931597</t>
+          <t>933803</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,92%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>126468</t>
+          <t>124755</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>168759</t>
+          <t>168968</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>152403</t>
+          <t>151206</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>197375</t>
+          <t>196301</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>289625</t>
+          <t>292825</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>355699</t>
+          <t>353156</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,54%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>500338</t>
+          <t>500129</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>542629</t>
+          <t>544342</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>464011</t>
+          <t>465085</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>508983</t>
+          <t>510180</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>974784</t>
+          <t>977327</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1040858</t>
+          <t>1037658</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>77,99%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>144412</t>
+          <t>145203</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>189582</t>
+          <t>191280</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>159465</t>
+          <t>156857</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>204570</t>
+          <t>203771</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>315835</t>
+          <t>314766</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>381129</t>
+          <t>383442</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,61%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>456466</t>
+          <t>454768</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>501636</t>
+          <t>500845</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>444507</t>
+          <t>445306</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>489612</t>
+          <t>492220</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>913996</t>
+          <t>911683</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>979290</t>
+          <t>980359</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>75,7%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>125450</t>
+          <t>123778</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>166033</t>
+          <t>164286</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>172640</t>
+          <t>172111</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>218148</t>
+          <t>220633</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>308239</t>
+          <t>309001</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>374244</t>
+          <t>373595</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>38,33%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>311885</t>
+          <t>313632</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>352468</t>
+          <t>354140</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>278701</t>
+          <t>276216</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>324209</t>
+          <t>324738</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>600523</t>
+          <t>601172</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>666528</t>
+          <t>665766</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>68,3%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>114836</t>
+          <t>113068</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>147797</t>
+          <t>150066</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>165386</t>
+          <t>165675</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>206634</t>
+          <t>205384</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>290656</t>
+          <t>289593</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>345240</t>
+          <t>341980</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>48,02%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>186533</t>
+          <t>184264</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>219494</t>
+          <t>221262</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>171128</t>
+          <t>172378</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>212376</t>
+          <t>212087</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>366852</t>
+          <t>370112</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>421436</t>
+          <t>422499</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>59,33%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>94870</t>
+          <t>94630</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>122601</t>
+          <t>123290</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>153628</t>
+          <t>152696</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>199227</t>
+          <t>198681</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>256378</t>
+          <t>253517</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>311948</t>
+          <t>309360</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>47,07%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>134397</t>
+          <t>133708</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>162128</t>
+          <t>162368</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>200942</t>
+          <t>201488</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>246541</t>
+          <t>247473</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>345219</t>
+          <t>347807</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>400789</t>
+          <t>403650</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>61,42%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>799914</t>
+          <t>810478</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>906779</t>
+          <t>907318</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1110662</t>
+          <t>1112386</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1227594</t>
+          <t>1217719</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1941723</t>
+          <t>1944005</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2090482</t>
+          <t>2099412</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,26%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2487571</t>
+          <t>2487032</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2594436</t>
+          <t>2583872</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2316948</t>
+          <t>2326823</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2433880</t>
+          <t>2432156</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4848410</t>
+          <t>4839480</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4997169</t>
+          <t>4994887</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>71,98%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>31210</t>
+          <t>28233</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15629</t>
+          <t>15049</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58490</t>
+          <t>47839</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>55060</t>
+          <t>65113</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38519</t>
+          <t>48588</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>76571</t>
+          <t>87945</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>86270</t>
+          <t>93347</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>62951</t>
+          <t>71390</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>117097</t>
+          <t>127397</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,54%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>368777</t>
+          <t>379560</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>341497</t>
+          <t>359954</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>384358</t>
+          <t>392744</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>258140</t>
+          <t>297399</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>236629</t>
+          <t>274567</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>274681</t>
+          <t>313924</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>626917</t>
+          <t>676958</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>596090</t>
+          <t>642908</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>650236</t>
+          <t>698915</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>90,73%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>78644</t>
+          <t>81752</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59413</t>
+          <t>62255</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>102201</t>
+          <t>103864</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>166114</t>
+          <t>110784</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>106692</t>
+          <t>93317</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>303343</t>
+          <t>131971</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>244758</t>
+          <t>192536</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>180437</t>
+          <t>165240</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>418175</t>
+          <t>224323</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>22,99%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>344903</t>
+          <t>395138</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>321346</t>
+          <t>373026</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>364134</t>
+          <t>414635</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>344107</t>
+          <t>387961</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>206878</t>
+          <t>366774</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>403529</t>
+          <t>405428</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>689010</t>
+          <t>783099</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>515593</t>
+          <t>751312</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>753331</t>
+          <t>810395</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>83,06%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>510221</t>
+          <t>498745</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>510221</t>
+          <t>498745</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>510221</t>
+          <t>498745</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>933768</t>
+          <t>975635</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>933768</t>
+          <t>975635</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>933768</t>
+          <t>975635</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>80701</t>
+          <t>92110</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>64430</t>
+          <t>73701</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>98447</t>
+          <t>111818</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>118499</t>
+          <t>134536</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>103545</t>
+          <t>118029</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>134135</t>
+          <t>152229</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>199199</t>
+          <t>226646</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>176488</t>
+          <t>200245</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>223961</t>
+          <t>256565</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,64%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>455637</t>
+          <t>528727</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>437891</t>
+          <t>509019</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>471908</t>
+          <t>547136</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>423969</t>
+          <t>487603</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>408333</t>
+          <t>469910</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>438923</t>
+          <t>504110</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>879607</t>
+          <t>1016330</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>854845</t>
+          <t>986411</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>902318</t>
+          <t>1042731</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,89%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>127008</t>
+          <t>140816</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57687</t>
+          <t>117061</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>184240</t>
+          <t>164674</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>167846</t>
+          <t>178541</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>142879</t>
+          <t>161380</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>190172</t>
+          <t>197852</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>294854</t>
+          <t>319357</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>178891</t>
+          <t>290960</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>363089</t>
+          <t>349762</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>24,34%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>760778</t>
+          <t>559801</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>703546</t>
+          <t>535943</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>830099</t>
+          <t>583556</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>544623</t>
+          <t>557914</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>522297</t>
+          <t>538603</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>569590</t>
+          <t>575075</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1305401</t>
+          <t>1117715</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1237166</t>
+          <t>1087310</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1421364</t>
+          <t>1146112</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>79,75%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712469</t>
+          <t>736455</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712469</t>
+          <t>736455</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712469</t>
+          <t>736455</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600255</t>
+          <t>1437072</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600255</t>
+          <t>1437072</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600255</t>
+          <t>1437072</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>138635</t>
+          <t>142122</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>121486</t>
+          <t>121734</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>158114</t>
+          <t>163015</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>138412</t>
+          <t>157809</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>125720</t>
+          <t>141436</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>155008</t>
+          <t>174569</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>277047</t>
+          <t>299931</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>252790</t>
+          <t>276646</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>302719</t>
+          <t>329628</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,07%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>422599</t>
+          <t>467224</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>403120</t>
+          <t>446331</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>439748</t>
+          <t>487612</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>409052</t>
+          <t>450600</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>392456</t>
+          <t>433840</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>421744</t>
+          <t>466973</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>831651</t>
+          <t>917824</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>805979</t>
+          <t>888127</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>855908</t>
+          <t>941109</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>75,37%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>72,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>77,28%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547464</t>
+          <t>608409</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547464</t>
+          <t>608409</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547464</t>
+          <t>608409</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1108698</t>
+          <t>1217755</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1108698</t>
+          <t>1217755</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1108698</t>
+          <t>1217755</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>104761</t>
+          <t>115706</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>91320</t>
+          <t>100316</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>118373</t>
+          <t>131915</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>122397</t>
+          <t>135282</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>47256</t>
+          <t>121639</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>192846</t>
+          <t>150571</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>227159</t>
+          <t>250987</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>110506</t>
+          <t>230226</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>293100</t>
+          <t>270778</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>32,06%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>262783</t>
+          <t>290706</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>249171</t>
+          <t>274497</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>276224</t>
+          <t>306096</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>484982</t>
+          <t>302898</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>414533</t>
+          <t>287609</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>560123</t>
+          <t>316541</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>747765</t>
+          <t>593605</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>681824</t>
+          <t>573814</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>864418</t>
+          <t>614366</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>72,74%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>367544</t>
+          <t>406412</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>367544</t>
+          <t>406412</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>367544</t>
+          <t>406412</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>607379</t>
+          <t>438180</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>607379</t>
+          <t>438180</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>607379</t>
+          <t>438180</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>974924</t>
+          <t>844592</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>974924</t>
+          <t>844592</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>974924</t>
+          <t>844592</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>80396</t>
+          <t>89886</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>68503</t>
+          <t>76542</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>92305</t>
+          <t>103534</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>128234</t>
+          <t>144554</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>115124</t>
+          <t>130041</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>142108</t>
+          <t>160089</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>208630</t>
+          <t>234440</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>189624</t>
+          <t>213340</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>225910</t>
+          <t>253640</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>32,79%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>201546</t>
+          <t>219407</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>189637</t>
+          <t>205759</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>213439</t>
+          <t>232751</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>297198</t>
+          <t>319633</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>283324</t>
+          <t>304098</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>310308</t>
+          <t>334146</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>498744</t>
+          <t>539039</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>481464</t>
+          <t>519839</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>517750</t>
+          <t>560139</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>69,69%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>72,42%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>281942</t>
+          <t>309293</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>281942</t>
+          <t>309293</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>281942</t>
+          <t>309293</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425432</t>
+          <t>464187</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425432</t>
+          <t>464187</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425432</t>
+          <t>464187</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>707374</t>
+          <t>773479</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>707374</t>
+          <t>773479</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>707374</t>
+          <t>773479</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>641355</t>
+          <t>690624</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>483831</t>
+          <t>642263</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>712631</t>
+          <t>746952</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>896562</t>
+          <t>926620</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>758693</t>
+          <t>881086</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1050300</t>
+          <t>972095</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1537917</t>
+          <t>1617244</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1355095</t>
+          <t>1547884</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1718603</t>
+          <t>1683892</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>23,19%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2817024</t>
+          <t>2840564</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2745748</t>
+          <t>2784236</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2974548</t>
+          <t>2888925</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2762071</t>
+          <t>2804006</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2608333</t>
+          <t>2758531</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2899940</t>
+          <t>2849540</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>5579095</t>
+          <t>5644570</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5398409</t>
+          <t>5577922</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5761917</t>
+          <t>5713930</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>78,68%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3458379</t>
+          <t>3531188</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3458379</t>
+          <t>3531188</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3458379</t>
+          <t>3531188</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3658633</t>
+          <t>3730626</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3658633</t>
+          <t>3730626</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3658633</t>
+          <t>3730626</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7117012</t>
+          <t>7261814</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7117012</t>
+          <t>7261814</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7117012</t>
+          <t>7261814</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
